--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-directive-anticipee.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-directive-anticipee.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6660" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6660" uniqueCount="535">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -848,6 +848,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -8563,7 +8567,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -8571,10 +8575,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8600,10 +8604,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8634,7 +8638,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8652,7 +8656,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8672,10 +8676,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8773,10 +8777,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8817,7 +8821,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8876,10 +8880,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8979,10 +8983,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9082,10 +9086,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9185,10 +9189,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9288,10 +9292,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9389,10 +9393,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9490,10 +9494,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9593,10 +9597,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9696,10 +9700,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9799,10 +9803,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9825,13 +9829,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9882,7 +9886,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9902,10 +9906,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9928,7 +9932,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9961,7 +9965,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9979,7 +9983,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9999,10 +10003,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10025,7 +10029,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -10078,7 +10082,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10098,10 +10102,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10157,25 +10161,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10195,10 +10199,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10221,13 +10225,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10278,7 +10282,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10298,10 +10302,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10324,7 +10328,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10357,25 +10361,25 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10395,10 +10399,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10421,7 +10425,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10454,25 +10458,25 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10492,10 +10496,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10522,7 +10526,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10573,7 +10577,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10593,10 +10597,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10619,7 +10623,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10672,7 +10676,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10692,10 +10696,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10718,7 +10722,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10771,7 +10775,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10791,10 +10795,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10817,7 +10821,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10870,7 +10874,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10890,10 +10894,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10916,7 +10920,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10969,7 +10973,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10989,10 +10993,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11015,7 +11019,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -11068,7 +11072,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -11088,10 +11092,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11114,7 +11118,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -11167,7 +11171,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11187,10 +11191,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11213,7 +11217,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11266,7 +11270,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11286,10 +11290,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11387,10 +11391,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11488,10 +11492,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11589,10 +11593,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11690,10 +11694,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11793,10 +11797,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11896,10 +11900,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11999,10 +12003,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12102,10 +12106,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12203,10 +12207,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12243,7 +12247,7 @@
         <v>74</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>74</v>
@@ -12262,7 +12266,7 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>74</v>
@@ -12280,7 +12284,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12300,10 +12304,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12330,7 +12334,7 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12381,7 +12385,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12401,10 +12405,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12431,12 +12435,12 @@
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
@@ -12482,7 +12486,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12502,10 +12506,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12581,7 +12585,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12601,10 +12605,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12627,7 +12631,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12680,7 +12684,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12700,10 +12704,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12726,7 +12730,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12779,7 +12783,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12799,10 +12803,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12825,7 +12829,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12878,7 +12882,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12898,10 +12902,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12924,7 +12928,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12977,7 +12981,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12997,10 +13001,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13023,7 +13027,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13076,7 +13080,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13096,10 +13100,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13122,13 +13126,13 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13179,7 +13183,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13199,10 +13203,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13300,10 +13304,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13401,10 +13405,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13502,10 +13506,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13603,10 +13607,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13706,10 +13710,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13809,10 +13813,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13912,10 +13916,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14015,10 +14019,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14116,10 +14120,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14142,7 +14146,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14195,7 +14199,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14215,10 +14219,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14292,7 +14296,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
@@ -14312,10 +14316,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14371,7 +14375,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -14389,7 +14393,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
@@ -14409,10 +14413,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14438,10 +14442,10 @@
         <v>95</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14492,7 +14496,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14512,10 +14516,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14571,7 +14575,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>74</v>
@@ -14589,7 +14593,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14609,10 +14613,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14638,7 +14642,7 @@
         <v>213</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -14690,7 +14694,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -14710,10 +14714,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14811,10 +14815,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14912,10 +14916,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15015,10 +15019,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15116,10 +15120,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15219,10 +15223,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15282,7 +15286,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15320,10 +15324,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15349,7 +15353,7 @@
         <v>85</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -15419,10 +15423,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15524,10 +15528,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15627,10 +15631,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15722,7 +15726,7 @@
         <v>74</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>74</v>
@@ -15730,10 +15734,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15756,7 +15760,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15809,7 +15813,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15829,10 +15833,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15855,7 +15859,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15908,7 +15912,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15928,10 +15932,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15954,7 +15958,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16007,7 +16011,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16027,10 +16031,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16053,7 +16057,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16106,7 +16110,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -16126,10 +16130,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16152,7 +16156,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16205,7 +16209,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16225,10 +16229,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16251,7 +16255,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16304,7 +16308,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16324,10 +16328,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16350,7 +16354,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16403,7 +16407,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16423,10 +16427,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16449,7 +16453,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16502,7 +16506,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16522,10 +16526,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16548,7 +16552,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16601,7 +16605,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16621,10 +16625,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16647,7 +16651,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16700,7 +16704,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16720,10 +16724,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16746,7 +16750,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16799,7 +16803,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16819,10 +16823,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16845,7 +16849,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16898,7 +16902,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16918,10 +16922,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16944,7 +16948,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16997,7 +17001,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -17017,10 +17021,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17043,7 +17047,7 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -17096,7 +17100,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -17116,10 +17120,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17142,7 +17146,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -17195,7 +17199,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17215,10 +17219,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17241,13 +17245,13 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17298,7 +17302,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17318,10 +17322,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17419,10 +17423,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17520,10 +17524,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17621,10 +17625,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17722,10 +17726,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17825,10 +17829,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17928,10 +17932,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18031,10 +18035,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18134,10 +18138,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18235,10 +18239,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18336,10 +18340,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18439,10 +18443,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18542,10 +18546,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18586,7 +18590,7 @@
         <v>74</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="T164" t="s" s="2">
         <v>74</v>
@@ -18645,10 +18649,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18748,10 +18752,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18788,7 +18792,7 @@
         <v>74</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>74</v>
@@ -18807,7 +18811,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>74</v>
@@ -18825,7 +18829,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
@@ -18845,10 +18849,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18871,7 +18875,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18924,7 +18928,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18944,10 +18948,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18970,7 +18974,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19023,7 +19027,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19043,10 +19047,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19069,7 +19073,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19122,7 +19126,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -19142,10 +19146,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19168,7 +19172,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19221,7 +19225,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19241,10 +19245,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19267,7 +19271,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19320,7 +19324,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19340,10 +19344,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19441,10 +19445,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19542,10 +19546,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19643,10 +19647,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19744,10 +19748,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19847,10 +19851,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19950,10 +19954,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20053,10 +20057,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20156,10 +20160,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20257,10 +20261,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20290,14 +20294,14 @@
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q181" s="2"/>
       <c r="R181" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>74</v>
@@ -20316,7 +20320,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>74</v>
@@ -20334,7 +20338,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20354,10 +20358,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20413,7 +20417,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>74</v>
@@ -20431,7 +20435,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -20451,10 +20455,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20480,10 +20484,10 @@
         <v>95</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20534,7 +20538,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20554,10 +20558,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20613,7 +20617,7 @@
       </c>
       <c r="Y184" s="2"/>
       <c r="Z184" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>74</v>
@@ -20631,7 +20635,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20651,10 +20655,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20680,7 +20684,7 @@
         <v>213</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
@@ -20732,7 +20736,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20752,10 +20756,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20853,10 +20857,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20954,10 +20958,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21057,10 +21061,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21158,10 +21162,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21261,10 +21265,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21362,10 +21366,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21459,10 +21463,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21564,10 +21568,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21667,10 +21671,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21762,7 +21766,7 @@
         <v>74</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>74</v>
@@ -21770,10 +21774,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21849,7 +21853,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -21869,10 +21873,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21895,7 +21899,7 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -21948,7 +21952,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -21968,10 +21972,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -21994,7 +21998,7 @@
         <v>74</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22047,7 +22051,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -22067,10 +22071,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22093,7 +22097,7 @@
         <v>74</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22146,7 +22150,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22166,10 +22170,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22192,7 +22196,7 @@
         <v>74</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22245,7 +22249,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22265,10 +22269,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22291,11 +22295,11 @@
         <v>74</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -22346,7 +22350,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22366,10 +22370,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22467,10 +22471,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22568,10 +22572,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22669,10 +22673,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22770,10 +22774,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22873,10 +22877,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22976,10 +22980,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23079,10 +23083,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23182,10 +23186,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23283,10 +23287,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23320,7 +23324,7 @@
       </c>
       <c r="Q211" s="2"/>
       <c r="R211" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="S211" t="s" s="2">
         <v>74</v>
@@ -23342,7 +23346,7 @@
       </c>
       <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>74</v>
@@ -23360,7 +23364,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23380,10 +23384,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23406,7 +23410,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23459,7 +23463,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>75</v>
@@ -23479,10 +23483,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23505,7 +23509,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23558,7 +23562,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
